--- a/booking_forms/045_facility_booking_form--booking_forms.xlsx
+++ b/booking_forms/045_facility_booking_form--booking_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1151,14 +1151,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>-_one-off_event
--_ongoing_use</t>
+          <t>-_one-off_event_-_ongoing_use</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>- One-off Event
-- Ongoing Use</t>
+          <t>- One-off Event - Ongoing Use</t>
         </is>
       </c>
     </row>
@@ -1187,16 +1185,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-_available
--_not_available
--_offline</t>
+          <t>-_available_-_not_available_-_offline</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>- Available
-- Not Available
-- Offline</t>
+          <t>- Available - Not Available - Offline</t>
         </is>
       </c>
     </row>
@@ -1225,18 +1219,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-_available
--_available
--_available
--_available</t>
+          <t>-_available_-_available_-_available_-_available</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>- Available
-- Available
-- Available
-- Available</t>
+          <t>- Available - Available - Available - Available</t>
         </is>
       </c>
     </row>
@@ -1265,16 +1253,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-_available
--_not_available
--_offline</t>
+          <t>-_available_-_not_available_-_offline</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>- Available
-- Not Available
-- Offline</t>
+          <t>- Available - Not Available - Offline</t>
         </is>
       </c>
     </row>
@@ -1303,14 +1287,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-_online_payment
--_offline_payment</t>
+          <t>-_online_payment_-_offline_payment</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>- Online Payment
-- Offline Payment</t>
+          <t>- Online Payment - Offline Payment</t>
         </is>
       </c>
     </row>
@@ -1339,16 +1321,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>-_credit_card
--_bank_transfer
--_cheque</t>
+          <t>-_credit_card_-_bank_transfer_-_cheque</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>- Credit Card
-- Bank Transfer
-- Cheque</t>
+          <t>- Credit Card - Bank Transfer - Cheque</t>
         </is>
       </c>
     </row>
@@ -1377,14 +1355,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>-_available
--_not_available</t>
+          <t>-_available_-_not_available</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>- Available
-- Not Available</t>
+          <t>- Available - Not Available</t>
         </is>
       </c>
     </row>
